--- a/spreadsheets/domains/cramps-fin_CRAMPS-FIN_Workbook.xlsx
+++ b/spreadsheets/domains/cramps-fin_CRAMPS-FIN_Workbook.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="1" r:id="R81ddba7540f14d2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Scope" sheetId="2" r:id="R926c97731fed4040"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Sources" sheetId="3" r:id="R2893d64850f34fc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Rows" sheetId="4" r:id="R1c52399f7aef4fc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gotchas" sheetId="5" r:id="Rd1ce2ceacec64ab6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Gate" sheetId="6" r:id="R8b8eb0076fe24ce7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Evidence Binder" sheetId="7" r:id="R6ff4e01a318b4e4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Log" sheetId="8" r:id="Rc842a31a1af94a84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trust Checkpoints" sheetId="9" r:id="Rd6073ef19e504067"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reliance Positioning" sheetId="10" r:id="R0b07c457871040cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="1" r:id="R9d77c7988f5f4516"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Scope" sheetId="2" r:id="Ra71779de4d2c4925"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Sources" sheetId="3" r:id="Reaafff2b27854366"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Rows" sheetId="4" r:id="R6086ca27a88d4418"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Failure Modes" sheetId="5" r:id="Rfe15366b3f23481d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Gate" sheetId="6" r:id="R2a486a317bdb48d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Evidence Binder" sheetId="7" r:id="Rc02500bc2618482f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Log" sheetId="8" r:id="R2c4bd051aeec4dee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trust Checkpoints" sheetId="9" r:id="R8d90cc8b0b3049c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reliance Positioning" sheetId="10" r:id="R4d008799e4fa4f73"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -250,7 +250,7 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
-        <x:v>Gotchas</x:v>
+        <x:v>Primary failure modes</x:v>
       </x:c>
       <x:c r="B7" t="str">
         <x:v>look-ahead bias; backtest overfitting; vendor revisions; feedback loops from prior controls</x:v>
@@ -1089,7 +1089,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str">
-        <x:v>Gotcha</x:v>
+        <x:v>Failure mode</x:v>
       </x:c>
       <x:c r="B1" t="str">
         <x:v>Status</x:v>
@@ -1255,7 +1255,7 @@
       <x:c r="B6" t="str"/>
       <x:c r="C6" t="str"/>
       <x:c r="D6" t="str">
-        <x:v>raw rows, source trace, extraction confidence, review status, quarantine log</x:v>
+        <x:v>raw signal rows, source trace, extraction confidence, review status, quarantine log</x:v>
       </x:c>
       <x:c r="E6" t="str"/>
     </x:row>
